--- a/Nhom_DAF15.xlsx
+++ b/Nhom_DAF15.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\project_mern\FInal_FullStack\final_fullstack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{979B2D9B-527F-47A1-8452-53FE18566386}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1C0CF2-7601-47AF-A2FB-D8C5DD488496}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bang danh gia" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="80">
   <si>
     <t>Tiêu chí đánh giá chung (Mỗi tiêu chí tối đa 0.5đ)</t>
   </si>
@@ -278,6 +278,15 @@
   </si>
   <si>
     <t>Lĩ Chính Hiền</t>
+  </si>
+  <si>
+    <t>Đăng nhập, đăng ký, quên mật khẩu, hồ sơ người dùng, giao diện màn hình chat</t>
+  </si>
+  <si>
+    <t>Xử lí sự kiện socket cho chat 1-1, chat group, thông tin đoạn chat, gọi video, triển khai docker compose, nginx</t>
+  </si>
+  <si>
+    <t>Chức năng bạn bè, giao diện, xử lí sự kiện socket bạn bè, báo cáo</t>
   </si>
 </sst>
 </file>
@@ -400,7 +409,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -478,6 +487,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -7586,21 +7596,39 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="25"/>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
+      <c r="A2" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>78</v>
+      </c>
+      <c r="C2" s="30">
+        <v>1</v>
+      </c>
       <c r="D2" s="25"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="25"/>
+      <c r="A3" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="30">
+        <v>1</v>
+      </c>
       <c r="D3" s="25"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="30">
+        <v>1</v>
+      </c>
       <c r="D4" s="25"/>
     </row>
     <row r="5" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
